--- a/reference/origins/product info/WA_PreRolls_50_Product_List_CBD_Lifestyle_Fixed.xlsx
+++ b/reference/origins/product info/WA_PreRolls_50_Product_List_CBD_Lifestyle_Fixed.xlsx
@@ -431,7 +431,7 @@
         <x:v>$6.99 / $11.99</x:v>
       </x:c>
       <x:c r="N2" s="14" t="str">
-        <x:v>Bright, aromatic flower with a clean grind and even burn; berry, citrus, and ...</x:v>
+        <x:v>Bright, aromatic flower with a clean grind and even burn; berry, citrus, and light pine carry through a smooth everyday smoke.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="34" customHeight="1">
@@ -469,7 +469,7 @@
         <x:v>$13.99</x:v>
       </x:c>
       <x:c r="N3" s="14" t="str">
-        <x:v>Dense, resinous flower with a slow burn and a pungent profile of sweet gas, f...</x:v>
+        <x:v>Dense, resinous flower with a slow burn and a pungent profile of sweet gas, floral spice, and marker-like funk.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
@@ -507,7 +507,7 @@
         <x:v>$9.99 / $12.99</x:v>
       </x:c>
       <x:c r="N4" s="14" t="str">
-        <x:v>Well-cured MAC 1 flower rolls tightly and burns pale and steady, layering cit...</x:v>
+        <x:v>Well-cured MAC 1 flower rolls tightly and burns pale and steady, layering citrus peel, cream, and earthy diesel.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -545,7 +545,7 @@
         <x:v>$7.99</x:v>
       </x:c>
       <x:c r="N5" s="14" t="str">
-        <x:v>Frosty flower with a lively resin ring and consistent draw; pine, lemon, and ...</x:v>
+        <x:v>Frosty flower with a lively resin ring and consistent draw; pine, lemon, and sharp fuel define the terpene profile.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
@@ -583,7 +583,7 @@
         <x:v>$6.99 / $9.49 / $12.49</x:v>
       </x:c>
       <x:c r="N6" s="14" t="str">
-        <x:v>Softly sweet, well-cured flower with vanilla dough and peppery earth, packed ...</x:v>
+        <x:v>Softly sweet, well-cured flower with vanilla dough and peppery earth, packed for an even, unhurried burn.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
@@ -621,7 +621,7 @@
         <x:v>$6.49 / $10.99</x:v>
       </x:c>
       <x:c r="N7" s="14" t="str">
-        <x:v>Colorful, fragrant flower with candy-fruit terpenes and creamy gas; the joint...</x:v>
+        <x:v>Colorful, fragrant flower with candy-fruit terpenes and creamy gas; the joint stays flavorful through the finish.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="34" customHeight="1">
@@ -659,7 +659,7 @@
         <x:v>$13.49</x:v>
       </x:c>
       <x:c r="N8" s="14" t="str">
-        <x:v>Sticky Gelato flower delivers a dense smoke with sweet cream, berry, and fuel...</x:v>
+        <x:v>Sticky Gelato flower delivers a dense smoke with sweet cream, berry, and fuel notes and a smooth, controlled burn.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
@@ -697,7 +697,7 @@
         <x:v>$10.49</x:v>
       </x:c>
       <x:c r="N9" s="14" t="str">
-        <x:v>Heavy trichome coverage and a rich cure produce a slow-burning joint with gar...</x:v>
+        <x:v>Heavy trichome coverage and a rich cure produce a slow-burning joint with garlic, earth, and savory diesel character.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="34" customHeight="1">
@@ -735,7 +735,7 @@
         <x:v>$8.49 / $14.49</x:v>
       </x:c>
       <x:c r="N10" s="14" t="str">
-        <x:v>Terpene-forward flower with orange peel, cherry, and earthy spice; finely fin...</x:v>
+        <x:v>Terpene-forward flower with orange peel, cherry, and earthy spice; finely finished for a clean draw and sturdy ash.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="34" customHeight="1">
@@ -773,7 +773,7 @@
         <x:v>$6.49 / $8.99 / $11.49</x:v>
       </x:c>
       <x:c r="N11" s="14" t="str">
-        <x:v>Classic Jack flower brings crisp pine, lemon zest, and herbal spice with an a...</x:v>
+        <x:v>Classic Jack flower brings crisp pine, lemon zest, and herbal spice with an airy grind that burns evenly.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="34" customHeight="1">
@@ -811,7 +811,7 @@
         <x:v>$14.49</x:v>
       </x:c>
       <x:c r="N12" s="14" t="str">
-        <x:v>Potent, sticky flower with lemon candy, dark cherry, and creamy gas aromas, r...</x:v>
+        <x:v>Potent, sticky flower with lemon candy, dark cherry, and creamy gas aromas, rolled for a rich and lingering smoke.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="34" customHeight="1">
@@ -849,7 +849,7 @@
         <x:v>$7.49</x:v>
       </x:c>
       <x:c r="N13" s="14" t="str">
-        <x:v>Fragrant sativa flower with anise, citrus, and fresh herb notes; a firm roll ...</x:v>
+        <x:v>Fragrant sativa flower with anise, citrus, and fresh herb notes; a firm roll supports an open draw and crisp burn.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="34" customHeight="1">
@@ -887,7 +887,7 @@
         <x:v>$79.99</x:v>
       </x:c>
       <x:c r="N14" s="14" t="str">
-        <x:v>A shareable pack of bright tropical flower joints with pineapple, cedar, and ...</x:v>
+        <x:v>A shareable pack of bright tropical flower joints with pineapple, cedar, and citrus aromas and dependable combustion.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="34" customHeight="1">
@@ -925,7 +925,7 @@
         <x:v>$74.99</x:v>
       </x:c>
       <x:c r="N15" s="14" t="str">
-        <x:v>Twenty compact flower joints built around orange, tangerine, and light floral...</x:v>
+        <x:v>Twenty compact flower joints built around orange, tangerine, and light floral terpenes with a clean, social-friendly burn.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -963,7 +963,7 @@
         <x:v>$9.49 / $11.99</x:v>
       </x:c>
       <x:c r="N16" s="14" t="str">
-        <x:v>Classic indica flower with sweet earth, pine, and subtle spice; the cure supp...</x:v>
+        <x:v>Classic indica flower with sweet earth, pine, and subtle spice; the cure supports a slow burn and soft smoke texture.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="34" customHeight="1">
@@ -1003,7 +1003,7 @@
         <x:v>$13.49 / $20.99</x:v>
       </x:c>
       <x:c r="N17" s="14" t="str">
-        <x:v>Biscotti flower is infused with aromatic live resin to deepen its cookie, spi...</x:v>
+        <x:v>Biscotti flower is infused with aromatic live resin to deepen its cookie, spice, and fuel profile without overwhelming the flower.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="34" customHeight="1">
@@ -1043,7 +1043,7 @@
         <x:v>$14.99</x:v>
       </x:c>
       <x:c r="N18" s="14" t="str">
-        <x:v>Two half-size joints use solventless rosin to amplify tart candy and citrus t...</x:v>
+        <x:v>Two half-size joints use solventless rosin to amplify tart candy and citrus terpenes while preserving a smooth, flower-led finish.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="34" customHeight="1">
@@ -1083,7 +1083,7 @@
         <x:v>$12.49 / $19.49</x:v>
       </x:c>
       <x:c r="N19" s="14" t="str">
-        <x:v>A measured distillate infusion raises potency while Gushers flower supplies t...</x:v>
+        <x:v>A measured distillate infusion raises potency while Gushers flower supplies tropical fruit, cream, and a lightly gassy backbone.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="34" customHeight="1">
@@ -1123,7 +1123,7 @@
         <x:v>$21.99</x:v>
       </x:c>
       <x:c r="N20" s="14" t="str">
-        <x:v>Full-flavored GMO flower and hash create a dense, slow smoke with savory garl...</x:v>
+        <x:v>Full-flavored GMO flower and hash create a dense, slow smoke with savory garlic, earth, and diesel from first light to finish.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="34" customHeight="1">
@@ -1163,7 +1163,7 @@
         <x:v>$13.99</x:v>
       </x:c>
       <x:c r="N21" s="14" t="str">
-        <x:v>Kief boosts the flower's resin content while keeping the creamy vanilla, pepp...</x:v>
+        <x:v>Kief boosts the flower's resin content while keeping the creamy vanilla, pepper, and earthy character recognizable and balanced.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="34" customHeight="1">
@@ -1203,7 +1203,7 @@
         <x:v>$17.49</x:v>
       </x:c>
       <x:c r="N22" s="14" t="str">
-        <x:v>Live resin complements carefully cured RS11 flower with louder berry, citrus,...</x:v>
+        <x:v>Live resin complements carefully cured RS11 flower with louder berry, citrus, and gas aromatics and a steady resin-rich burn.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="34" customHeight="1">
@@ -1243,7 +1243,7 @@
         <x:v>$12.99</x:v>
       </x:c>
       <x:c r="N23" s="14" t="str">
-        <x:v>Compact infused joint pairing fruity Zkittlez flower with distillate for high...</x:v>
+        <x:v>Compact infused joint pairing fruity Zkittlez flower with distillate for higher potency, easy draw, and a sweet candy-forward smoke.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="34" customHeight="1">
@@ -1283,7 +1283,7 @@
         <x:v>$19.99</x:v>
       </x:c>
       <x:c r="N24" s="14" t="str">
-        <x:v>A three-part build of Permanent Marker flower, terpene-rich live resin, and k...</x:v>
+        <x:v>A three-part build of Permanent Marker flower, terpene-rich live resin, and kief creates a layered floral-gas profile and dense smoke.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="34" customHeight="1">
@@ -1323,7 +1323,7 @@
         <x:v>$23.99</x:v>
       </x:c>
       <x:c r="N25" s="14" t="str">
-        <x:v>Animal Face flower is paired with solventless rosin and hash for concentrated...</x:v>
+        <x:v>Animal Face flower is paired with solventless rosin and hash for concentrated pine, citrus, and fuel with a deliberate slow burn.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
@@ -1363,7 +1363,7 @@
         <x:v>$28.99</x:v>
       </x:c>
       <x:c r="N26" s="18" t="str">
-        <x:v>Flower, distillate, and a kief finish combine into a high-potency joint that ...</x:v>
+        <x:v>Flower, distillate, and a kief finish combine into a high-potency joint that keeps lemon-cherry sweetness present beneath the richer infusion.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="34" customHeight="1">
@@ -1401,7 +1401,7 @@
         <x:v>$6.49 / $10.49</x:v>
       </x:c>
       <x:c r="N27" s="14" t="str">
-        <x:v>CBD-forward Harlequin flower offers mango, pine, and herbal notes with a ligh...</x:v>
+        <x:v>CBD-forward Harlequin flower offers mango, pine, and herbal notes with a light-bodied smoke and an easy, even burn.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="34" customHeight="1">
@@ -1439,7 +1439,7 @@
         <x:v>$6.99</x:v>
       </x:c>
       <x:c r="N28" s="14" t="str">
-        <x:v>A CBD-rich roll with airy, well-cured flower and gentle citrus, wood, and pep...</x:v>
+        <x:v>A CBD-rich roll with airy, well-cured flower and gentle citrus, wood, and pepper aromatics that remain clear through the finish.</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="34" customHeight="1">
@@ -1477,7 +1477,7 @@
         <x:v>$8.99 / $10.99</x:v>
       </x:c>
       <x:c r="N29" s="14" t="str">
-        <x:v>Balanced-looking resin coverage and a clean cure highlight earthy citrus and ...</x:v>
+        <x:v>Balanced-looking resin coverage and a clean cure highlight earthy citrus and light pine in this smooth-burning CBD cultivar.</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="34" customHeight="1">
@@ -1515,7 +1515,7 @@
         <x:v>$11.49</x:v>
       </x:c>
       <x:c r="N30" s="14" t="str">
-        <x:v>Sour citrus, pine, and faint diesel lead a flavorful CBD-forward joint made f...</x:v>
+        <x:v>Sour citrus, pine, and faint diesel lead a flavorful CBD-forward joint made from flower selected for consistency and clean combustion.</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="34" customHeight="1">
@@ -1553,7 +1553,7 @@
         <x:v>$6.49 / $8.49 / $10.99</x:v>
       </x:c>
       <x:c r="N31" s="14" t="str">
-        <x:v>CBD-rich flower with earthy mint and citrus aromatics, packed with an even te...</x:v>
+        <x:v>CBD-rich flower with earthy mint and citrus aromatics, packed with an even texture that keeps airflow consistent across all three sizes.</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="34" customHeight="1">
@@ -1591,7 +1591,7 @@
         <x:v>$7.99</x:v>
       </x:c>
       <x:c r="N32" s="14" t="str">
-        <x:v>Two compact CBD flower joints featuring soft lemon, pine, and floral notes wi...</x:v>
+        <x:v>Two compact CBD flower joints featuring soft lemon, pine, and floral notes with a mellow smoke texture and tidy ash.</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="34" customHeight="1">
@@ -1629,7 +1629,7 @@
         <x:v>$10.49</x:v>
       </x:c>
       <x:c r="N33" s="14" t="str">
-        <x:v>Fragrant CBD flower brings sweet funk, citrus, and a touch of fuel, with a sp...</x:v>
+        <x:v>Fragrant CBD flower brings sweet funk, citrus, and a touch of fuel, with a springy grind and reliable burn from tip to filter.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="34" customHeight="1">
@@ -1667,7 +1667,7 @@
         <x:v>$9.49</x:v>
       </x:c>
       <x:c r="N34" s="14" t="str">
-        <x:v>Tropical and floral CBD flower with pineapple-like sweetness and fresh herbs,...</x:v>
+        <x:v>Tropical and floral CBD flower with pineapple-like sweetness and fresh herbs, rolled to keep the smoke light and aromatic.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="34" customHeight="1">
@@ -1705,7 +1705,7 @@
         <x:v>$6.99 / $11.99</x:v>
       </x:c>
       <x:c r="N35" s="14" t="str">
-        <x:v>A resinous CBD cultivar with citrus peel, green fruit, and peppery herbs; the...</x:v>
+        <x:v>A resinous CBD cultivar with citrus peel, green fruit, and peppery herbs; the joint burns steadily without masking the flower.</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="34" customHeight="1">
@@ -1743,7 +1743,7 @@
         <x:v>$69.99</x:v>
       </x:c>
       <x:c r="N36" s="14" t="str">
-        <x:v>Twenty CBD-rich flower joints with tart fruit, sweet citrus, and light diesel...</x:v>
+        <x:v>Twenty CBD-rich flower joints with tart fruit, sweet citrus, and light diesel, portioned for consistent draws across the pack.</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="34" customHeight="1">
@@ -1783,7 +1783,7 @@
         <x:v>$13.99</x:v>
       </x:c>
       <x:c r="N37" s="14" t="str">
-        <x:v>Harlequin flower receives a light live-resin infusion that intensifies mango,...</x:v>
+        <x:v>Harlequin flower receives a light live-resin infusion that intensifies mango, pine, and citrus aromatics while retaining CBD prominence.</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="34" customHeight="1">
@@ -1823,7 +1823,7 @@
         <x:v>$14.49</x:v>
       </x:c>
       <x:c r="N38" s="14" t="str">
-        <x:v>Solventless rosin adds body and terpene depth to CBD-rich ACDC flower, produc...</x:v>
+        <x:v>Solventless rosin adds body and terpene depth to CBD-rich ACDC flower, producing a smooth citrus-wood smoke with a richer finish.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="34" customHeight="1">
@@ -1863,7 +1863,7 @@
         <x:v>$19.99</x:v>
       </x:c>
       <x:c r="N39" s="14" t="str">
-        <x:v>CBD-forward Cannatonic flower is reinforced with a measured distillate infusi...</x:v>
+        <x:v>CBD-forward Cannatonic flower is reinforced with a measured distillate infusion for higher cannabinoid content and a clean, controlled burn.</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="34" customHeight="1">
@@ -1903,7 +1903,7 @@
         <x:v>$18.49</x:v>
       </x:c>
       <x:c r="N40" s="14" t="str">
-        <x:v>Hash deepens Sour Tsunami's resin character while preserving sour citrus and ...</x:v>
+        <x:v>Hash deepens Sour Tsunami's resin character while preserving sour citrus and pine, giving the joint a slower, fuller-bodied smoke.</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="34" customHeight="1">
@@ -1943,7 +1943,7 @@
         <x:v>$13.49</x:v>
       </x:c>
       <x:c r="N41" s="18" t="str">
-        <x:v>A kief-enhanced pair built around CBD-rich Ringo's Gift flower, with earthy m...</x:v>
+        <x:v>A kief-enhanced pair built around CBD-rich Ringo's Gift flower, with earthy mint, citrus, and a dry, resinous finish.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="34" customHeight="1">
@@ -1981,7 +1981,7 @@
         <x:v>$6.99 / $11.49</x:v>
       </x:c>
       <x:c r="N42" s="14" t="str">
-        <x:v>Mixed-cannabinoid Harlequin flower combines moderate THC and CBD with mango, ...</x:v>
+        <x:v>Mixed-cannabinoid Harlequin flower combines moderate THC and CBD with mango, pine, and herbal terpenes in a smooth daily-style roll.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="34" customHeight="1">
@@ -2019,7 +2019,7 @@
         <x:v>$9.49</x:v>
       </x:c>
       <x:c r="N43" s="14" t="str">
-        <x:v>Cannatonic flower carries meaningful THC and CBD percentages alongside citrus...</x:v>
+        <x:v>Cannatonic flower carries meaningful THC and CBD percentages alongside citrus, earth, and pine, with a soft smoke and even burn.</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="34" customHeight="1">
@@ -2057,7 +2057,7 @@
         <x:v>$6.49 / $8.99 / $11.49</x:v>
       </x:c>
       <x:c r="N44" s="14" t="str">
-        <x:v>A mixed-cannabinoid flower profile with pepper, coffee, and subtle sweetness;...</x:v>
+        <x:v>A mixed-cannabinoid flower profile with pepper, coffee, and subtle sweetness; consistent cure supports all three joint sizes.</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="34" customHeight="1">
@@ -2095,7 +2095,7 @@
         <x:v>$11.99</x:v>
       </x:c>
       <x:c r="N45" s="14" t="str">
-        <x:v>Bright Dancehall flower offers tropical fruit, spice, and fresh herbs with su...</x:v>
+        <x:v>Bright Dancehall flower offers tropical fruit, spice, and fresh herbs with substantial THC and CBD shown directly on the product card.</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="34" customHeight="1">
@@ -2133,7 +2133,7 @@
         <x:v>$7.99</x:v>
       </x:c>
       <x:c r="N46" s="14" t="str">
-        <x:v>Two compact mixed-cannabinoid joints with sweet citrus, earthy spice, and a l...</x:v>
+        <x:v>Two compact mixed-cannabinoid joints with sweet citrus, earthy spice, and a light woody finish, rolled from evenly milled flower.</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="34" customHeight="1">
@@ -2171,7 +2171,7 @@
         <x:v>$7.49 / $12.49</x:v>
       </x:c>
       <x:c r="N47" s="14" t="str">
-        <x:v>Dense mixed-cannabinoid flower with honeyed earth, citrus, and mild skunk; a ...</x:v>
+        <x:v>Dense mixed-cannabinoid flower with honeyed earth, citrus, and mild skunk; a firm pack keeps the burn controlled and flavorful.</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="34" customHeight="1">
@@ -2209,7 +2209,7 @@
         <x:v>$9.99 / $12.49</x:v>
       </x:c>
       <x:c r="N48" s="14" t="str">
-        <x:v>Sour Tsunami flower presents both THC and CBD with sharp citrus, pine, and di...</x:v>
+        <x:v>Sour Tsunami flower presents both THC and CBD with sharp citrus, pine, and diesel aromatics and a clean-burning finish.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="34" customHeight="1">
@@ -2249,7 +2249,7 @@
         <x:v>$14.99</x:v>
       </x:c>
       <x:c r="N49" s="14" t="str">
-        <x:v>Live resin lifts the terpene profile of mixed-cannabinoid Pennywise flower, e...</x:v>
+        <x:v>Live resin lifts the terpene profile of mixed-cannabinoid Pennywise flower, emphasizing pepper, roasted sweetness, and subtle fruit.</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="34" customHeight="1">
@@ -2289,7 +2289,7 @@
         <x:v>$20.99</x:v>
       </x:c>
       <x:c r="N50" s="14" t="str">
-        <x:v>Cannatonic flower is infused for added potency while retaining clearly listed...</x:v>
+        <x:v>Cannatonic flower is infused for added potency while retaining clearly listed THC and CBD percentages and its citrus-earth character.</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="34" customHeight="1">
@@ -2329,7 +2329,7 @@
         <x:v>$14.49</x:v>
       </x:c>
       <x:c r="N51" s="18" t="str">
-        <x:v>A solventless rosin infusion enriches Harlequin's mango, pine, and herbal not...</x:v>
+        <x:v>A solventless rosin infusion enriches Harlequin's mango, pine, and herbal notes while maintaining a mixed THC-and-CBD cannabinoid profile.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
